--- a/ReportDefs-KINESYS_S100D.xlsx
+++ b/ReportDefs-KINESYS_S100D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5102FED8-BA9D-483B-B601-2667F709CD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7DE945-DCF9-48C0-9544-24553DD71C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,7 +364,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="1150">
   <si>
     <t>KS</t>
   </si>
@@ -7624,6 +7624,10 @@
       <c r="O8" t="s">
         <v>67</v>
       </c>
+      <c r="P8" t="str">
+        <f>P7</f>
+        <v>Elec_Prod</v>
+      </c>
       <c r="Q8" t="s">
         <v>68</v>
       </c>
@@ -7733,6 +7737,9 @@
       <c r="Q12" t="str">
         <f t="shared" ref="Q12:Q20" si="5">P12</f>
         <v>Capacity_Elec</v>
+      </c>
+      <c r="R12" t="s">
+        <v>84</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>90</v>

--- a/ReportDefs-KINESYS_S100D.xlsx
+++ b/ReportDefs-KINESYS_S100D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7DE945-DCF9-48C0-9544-24553DD71C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6155E3-F173-40A7-B737-22DF16A155B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,7 +364,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="1150">
   <si>
     <t>KS</t>
   </si>
@@ -3827,7 +3827,7 @@
     <numFmt numFmtId="167" formatCode="#."/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3958,6 +3958,14 @@
       <sz val="8"/>
       <name val="Tahoma"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -4098,7 +4106,7 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="3"/>
@@ -4119,6 +4127,7 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="Bad" xfId="4" builtinId="27"/>
@@ -7585,6 +7594,9 @@
       <c r="E7" s="17" t="s">
         <v>65</v>
       </c>
+      <c r="I7" s="18" t="s">
+        <v>54</v>
+      </c>
       <c r="J7" s="12" t="s">
         <v>1146</v>
       </c>
@@ -7601,9 +7613,6 @@
       <c r="Q7" t="s">
         <v>68</v>
       </c>
-      <c r="R7" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8" t="s">
@@ -7631,9 +7640,6 @@
       <c r="Q8" t="s">
         <v>68</v>
       </c>
-      <c r="R8" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9" t="s">
@@ -7737,9 +7743,6 @@
       <c r="Q12" t="str">
         <f t="shared" ref="Q12:Q20" si="5">P12</f>
         <v>Capacity_Elec</v>
-      </c>
-      <c r="R12" t="s">
-        <v>84</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>90</v>
